--- a/Results/5th Sem Results AIML1.xlsx
+++ b/Results/5th Sem Results AIML1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Imp\Coding\Python\Projects\Selenium\RGPV Result Bot\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC301172-36EC-4A35-B596-73D400843FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9BC60F-7195-4CF3-8058-3D0C46FCC85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{6B8163A5-99D5-42D5-BAE9-C4DDFFD45228}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="224">
   <si>
     <t>Roll No.</t>
   </si>
@@ -37,18 +37,6 @@
   </si>
   <si>
     <t>CGPA</t>
-  </si>
-  <si>
-    <t>AL-401</t>
-  </si>
-  <si>
-    <t>AL-402</t>
-  </si>
-  <si>
-    <t>AL-403</t>
-  </si>
-  <si>
-    <t>AL-404</t>
   </si>
   <si>
     <t>0827AL221080</t>
@@ -1300,10 +1288,10 @@
     <tableColumn id="3" xr3:uid="{0463C325-FD6C-4FE8-8918-26C8F2605C25}" name="Result"/>
     <tableColumn id="4" xr3:uid="{746E8826-D8A4-41FB-A7DD-55F8E9C3019F}" name="SGPA"/>
     <tableColumn id="5" xr3:uid="{375B7D44-12C5-4502-828D-BEA2CF7B8AFC}" name="CGPA"/>
-    <tableColumn id="6" xr3:uid="{A7BC5854-9F9D-4F9D-8DB8-825A6228A97B}" name="AL-401"/>
-    <tableColumn id="7" xr3:uid="{BE93E312-349F-4D81-96B2-1E06F5648ECE}" name="AL-402"/>
-    <tableColumn id="8" xr3:uid="{E6232ABD-46A0-44B4-B4AC-BA1BD7D72CD8}" name="AL-403"/>
-    <tableColumn id="9" xr3:uid="{48976C91-326B-4113-A0F1-3D2159916C55}" name="AL-404"/>
+    <tableColumn id="6" xr3:uid="{A7BC5854-9F9D-4F9D-8DB8-825A6228A97B}" name="AL-501"/>
+    <tableColumn id="7" xr3:uid="{BE93E312-349F-4D81-96B2-1E06F5648ECE}" name="AL-502"/>
+    <tableColumn id="8" xr3:uid="{E6232ABD-46A0-44B4-B4AC-BA1BD7D72CD8}" name="AL-503"/>
+    <tableColumn id="9" xr3:uid="{48976C91-326B-4113-A0F1-3D2159916C55}" name="AL-504"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1651,27 +1639,27 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>7.38</v>
@@ -1680,27 +1668,27 @@
         <v>7.28</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>8.92</v>
@@ -1709,27 +1697,27 @@
         <v>8.4600000000000009</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>7.63</v>
@@ -1738,27 +1726,27 @@
         <v>7.21</v>
       </c>
       <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="G4" t="s">
-        <v>16</v>
-      </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>7.29</v>
@@ -1767,27 +1755,27 @@
         <v>6.74</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>6.38</v>
@@ -1796,27 +1784,27 @@
         <v>5.7</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>7.46</v>
@@ -1825,27 +1813,27 @@
         <v>6.54</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>7.5</v>
@@ -1854,27 +1842,27 @@
         <v>6.46</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -1883,27 +1871,27 @@
         <v>6.59</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>6.71</v>
@@ -1912,27 +1900,27 @@
         <v>5.85</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>6.71</v>
@@ -1941,27 +1929,27 @@
         <v>6.4</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>6.17</v>
@@ -1970,27 +1958,27 @@
         <v>5.58</v>
       </c>
       <c r="F12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>7.29</v>
@@ -1999,27 +1987,27 @@
         <v>6.21</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I13" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D14">
         <v>7.92</v>
@@ -2028,27 +2016,27 @@
         <v>7.12</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <v>8.2100000000000009</v>
@@ -2057,27 +2045,27 @@
         <v>7</v>
       </c>
       <c r="F15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" t="s">
         <v>12</v>
       </c>
-      <c r="G15" t="s">
-        <v>16</v>
-      </c>
       <c r="H15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>6.92</v>
@@ -2086,27 +2074,27 @@
         <v>6.72</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H16" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I16" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>6.67</v>
@@ -2115,27 +2103,27 @@
         <v>6.28</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D18">
         <v>7.46</v>
@@ -2144,27 +2132,27 @@
         <v>7.17</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I18" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <v>8.67</v>
@@ -2173,27 +2161,27 @@
         <v>8.02</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -2202,27 +2190,27 @@
         <v>6.97</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I20" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>6.67</v>
@@ -2231,27 +2219,27 @@
         <v>6.03</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H21" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <v>6.88</v>
@@ -2260,27 +2248,27 @@
         <v>6.54</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I22" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>6.92</v>
@@ -2289,27 +2277,27 @@
         <v>6.55</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H23" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D24">
         <v>7.96</v>
@@ -2318,27 +2306,27 @@
         <v>7.05</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I24" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D25">
         <v>7.33</v>
@@ -2347,27 +2335,27 @@
         <v>6.91</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H25" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>7.5</v>
@@ -2376,27 +2364,27 @@
         <v>7.47</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H26" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <v>7.67</v>
@@ -2405,27 +2393,27 @@
         <v>6.97</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D28">
         <v>7.04</v>
@@ -2434,27 +2422,27 @@
         <v>6.78</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G28" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D29">
         <v>8.08</v>
@@ -2463,27 +2451,27 @@
         <v>7.46</v>
       </c>
       <c r="F29" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" t="s">
         <v>12</v>
       </c>
-      <c r="G29" t="s">
-        <v>16</v>
-      </c>
       <c r="H29" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I29" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>8</v>
@@ -2492,27 +2480,27 @@
         <v>7.4</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I30" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -2521,27 +2509,27 @@
         <v>5.57</v>
       </c>
       <c r="F31" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H31" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I31" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D32">
         <v>8.3800000000000008</v>
@@ -2550,27 +2538,27 @@
         <v>7.41</v>
       </c>
       <c r="F32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" t="s">
         <v>12</v>
       </c>
-      <c r="G32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H32" t="s">
-        <v>16</v>
-      </c>
       <c r="I32" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D33">
         <v>6.96</v>
@@ -2579,27 +2567,27 @@
         <v>6.26</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G33" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I33" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D34">
         <v>7.63</v>
@@ -2608,27 +2596,27 @@
         <v>6.89</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D35">
         <v>6.29</v>
@@ -2637,27 +2625,27 @@
         <v>5.6</v>
       </c>
       <c r="F35" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H35" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I35" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D36">
         <v>7.5</v>
@@ -2666,27 +2654,27 @@
         <v>6.96</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G36" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I36" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C37" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D37">
         <v>7.08</v>
@@ -2695,27 +2683,27 @@
         <v>7.09</v>
       </c>
       <c r="F37" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G37" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D38">
         <v>7.75</v>
@@ -2724,27 +2712,27 @@
         <v>7.33</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D39">
         <v>8.33</v>
@@ -2753,27 +2741,27 @@
         <v>7.39</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G39" t="s">
+        <v>8</v>
+      </c>
+      <c r="H39" t="s">
         <v>12</v>
       </c>
-      <c r="H39" t="s">
-        <v>16</v>
-      </c>
       <c r="I39" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B40" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D40">
         <v>7.04</v>
@@ -2782,27 +2770,27 @@
         <v>6.51</v>
       </c>
       <c r="F40" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G40" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I40" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C41" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <v>6.29</v>
@@ -2811,27 +2799,27 @@
         <v>6.25</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D42">
         <v>6.13</v>
@@ -2840,27 +2828,27 @@
         <v>6</v>
       </c>
       <c r="F42" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I42" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B43" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D43">
         <v>6.79</v>
@@ -2869,27 +2857,27 @@
         <v>5.96</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H43" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B44" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C44" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D44">
         <v>6.04</v>
@@ -2898,27 +2886,27 @@
         <v>5.55</v>
       </c>
       <c r="F44" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H44" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I44" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D45">
         <v>7.92</v>
@@ -2927,27 +2915,27 @@
         <v>7.43</v>
       </c>
       <c r="F45" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G45" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H45" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D46">
         <v>7.46</v>
@@ -2956,27 +2944,27 @@
         <v>6.76</v>
       </c>
       <c r="F46" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G46" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H46" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I46" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C47" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D47">
         <v>7.54</v>
@@ -2985,27 +2973,27 @@
         <v>6.86</v>
       </c>
       <c r="F47" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G47" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H47" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C48" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D48">
         <v>6.38</v>
@@ -3014,27 +3002,27 @@
         <v>6.1</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H48" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B49" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D49">
         <v>6.13</v>
@@ -3043,27 +3031,27 @@
         <v>6.05</v>
       </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G49" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H49" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I49" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B50" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C50" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D50">
         <v>7.17</v>
@@ -3072,27 +3060,27 @@
         <v>6.48</v>
       </c>
       <c r="F50" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H50" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B51" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C51" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D51">
         <v>8.08</v>
@@ -3101,27 +3089,27 @@
         <v>7.39</v>
       </c>
       <c r="F51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G51" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B52" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C52" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D52">
         <v>7.54</v>
@@ -3130,27 +3118,27 @@
         <v>6.6</v>
       </c>
       <c r="F52" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G52" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H52" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I52" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B53" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C53" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D53">
         <v>7.79</v>
@@ -3159,27 +3147,27 @@
         <v>6.62</v>
       </c>
       <c r="F53" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G53" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H53" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I53" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B54" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C54" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D54">
         <v>7.71</v>
@@ -3188,27 +3176,27 @@
         <v>7.03</v>
       </c>
       <c r="F54" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G54" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H54" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I54" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B55" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C55" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D55">
         <v>7</v>
@@ -3217,27 +3205,27 @@
         <v>6.3</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H55" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I55" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B56" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C56" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D56">
         <v>7.38</v>
@@ -3246,27 +3234,27 @@
         <v>6.74</v>
       </c>
       <c r="F56" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G56" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H56" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I56" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B57" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C57" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D57">
         <v>7.17</v>
@@ -3275,27 +3263,27 @@
         <v>6.44</v>
       </c>
       <c r="F57" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B58" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C58" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D58">
         <v>5.96</v>
@@ -3304,27 +3292,27 @@
         <v>5.79</v>
       </c>
       <c r="F58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B59" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C59" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D59">
         <v>7.46</v>
@@ -3333,27 +3321,27 @@
         <v>6.81</v>
       </c>
       <c r="F59" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G59" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H59" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B60" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C60" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D60">
         <v>7.42</v>
@@ -3362,27 +3350,27 @@
         <v>6.09</v>
       </c>
       <c r="F60" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G60" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H60" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I60" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C61" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D61">
         <v>6.33</v>
@@ -3391,27 +3379,27 @@
         <v>6.25</v>
       </c>
       <c r="F61" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B62" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C62" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D62">
         <v>8.5</v>
@@ -3420,27 +3408,27 @@
         <v>7.13</v>
       </c>
       <c r="F62" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G62" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H62" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I62" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B63" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C63" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D63">
         <v>6.96</v>
@@ -3449,27 +3437,27 @@
         <v>6.83</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B64" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C64" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D64">
         <v>6.75</v>
@@ -3478,27 +3466,27 @@
         <v>6.35</v>
       </c>
       <c r="F64" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H64" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I64" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B65" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C65" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D65">
         <v>7.17</v>
@@ -3507,27 +3495,27 @@
         <v>6.68</v>
       </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G65" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H65" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I65" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B66" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C66" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D66">
         <v>5.29</v>
@@ -3536,27 +3524,27 @@
         <v>5.19</v>
       </c>
       <c r="F66" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H66" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I66" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B67" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C67" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D67">
         <v>7.38</v>
@@ -3565,27 +3553,27 @@
         <v>6.8</v>
       </c>
       <c r="F67" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G67" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H67" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I67" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B68" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C68" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D68">
         <v>6.38</v>
@@ -3594,27 +3582,27 @@
         <v>5.96</v>
       </c>
       <c r="F68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H68" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B69" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C69" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D69">
         <v>7.54</v>
@@ -3623,27 +3611,27 @@
         <v>6.89</v>
       </c>
       <c r="F69" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G69" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H69" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I69" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B70" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C70" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D70">
         <v>7.71</v>
@@ -3652,27 +3640,27 @@
         <v>7.18</v>
       </c>
       <c r="F70" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G70" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H70" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I70" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B71" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C71" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D71">
         <v>6.63</v>
@@ -3681,27 +3669,27 @@
         <v>6.26</v>
       </c>
       <c r="F71" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G71" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H71" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I71" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B72" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C72" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D72">
         <v>6.88</v>
@@ -3710,27 +3698,27 @@
         <v>6.71</v>
       </c>
       <c r="F72" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G72" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H72" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B73" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C73" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D73">
         <v>7.29</v>
@@ -3739,27 +3727,27 @@
         <v>6.41</v>
       </c>
       <c r="F73" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G73" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H73" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I73" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B74" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C74" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D74">
         <v>6.17</v>
@@ -3768,27 +3756,27 @@
         <v>5.34</v>
       </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G74" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H74" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I74" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B75" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C75" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D75">
         <v>7.96</v>
@@ -3797,27 +3785,27 @@
         <v>6.98</v>
       </c>
       <c r="F75" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G75" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H75" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I75" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B76" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C76" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D76">
         <v>5.58</v>
@@ -3826,27 +3814,27 @@
         <v>5.69</v>
       </c>
       <c r="F76" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H76" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C77" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D77">
         <v>8.2100000000000009</v>
@@ -3855,27 +3843,27 @@
         <v>7.91</v>
       </c>
       <c r="F77" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G77" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H77" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I77" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B78" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C78" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D78">
         <v>6.63</v>
@@ -3884,27 +3872,27 @@
         <v>5.71</v>
       </c>
       <c r="F78" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G78" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H78" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I78" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B79" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C79" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D79">
         <v>8.08</v>
@@ -3913,27 +3901,27 @@
         <v>7.47</v>
       </c>
       <c r="F79" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G79" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H79" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I79" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B80" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C80" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D80">
         <v>7.5</v>
@@ -3942,27 +3930,27 @@
         <v>6.38</v>
       </c>
       <c r="F80" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G80" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H80" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I80" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B81" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C81" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D81">
         <v>6.33</v>
@@ -3971,27 +3959,27 @@
         <v>5.95</v>
       </c>
       <c r="F81" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H81" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I81" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B82" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C82" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D82">
         <v>8.17</v>
@@ -4000,27 +3988,27 @@
         <v>7.56</v>
       </c>
       <c r="F82" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G82" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H82" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I82" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B83" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C83" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D83">
         <v>7.96</v>
@@ -4029,27 +4017,27 @@
         <v>7.68</v>
       </c>
       <c r="F83" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G83" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H83" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I83" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B84" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C84" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D84">
         <v>7.04</v>
@@ -4058,27 +4046,27 @@
         <v>6.12</v>
       </c>
       <c r="F84" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G84" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H84" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I84" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B85" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C85" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D85">
         <v>7.42</v>
@@ -4087,27 +4075,27 @@
         <v>6.56</v>
       </c>
       <c r="F85" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G85" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H85" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I85" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B86" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C86" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D86">
         <v>7.38</v>
@@ -4116,27 +4104,27 @@
         <v>6.79</v>
       </c>
       <c r="F86" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G86" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H86" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I86" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B87" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C87" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D87">
         <v>7.17</v>
@@ -4145,27 +4133,27 @@
         <v>6.33</v>
       </c>
       <c r="F87" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G87" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H87" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I87" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B88" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C88" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D88">
         <v>8.0399999999999991</v>
@@ -4174,27 +4162,27 @@
         <v>7.77</v>
       </c>
       <c r="F88" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G88" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H88" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I88" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B89" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C89" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D89">
         <v>7.71</v>
@@ -4203,27 +4191,27 @@
         <v>7.3</v>
       </c>
       <c r="F89" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G89" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H89" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I89" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B90" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C90" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D90">
         <v>7.04</v>
@@ -4232,27 +4220,27 @@
         <v>6.3</v>
       </c>
       <c r="F90" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G90" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H90" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I90" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B91" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C91" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D91">
         <v>7.38</v>
@@ -4261,27 +4249,27 @@
         <v>6.93</v>
       </c>
       <c r="F91" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G91" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H91" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B92" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C92" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D92">
         <v>7.17</v>
@@ -4290,27 +4278,27 @@
         <v>6.66</v>
       </c>
       <c r="F92" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G92" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H92" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I92" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B93" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C93" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D93">
         <v>7.88</v>
@@ -4319,27 +4307,27 @@
         <v>7.31</v>
       </c>
       <c r="F93" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G93" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H93" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I93" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B94" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C94" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D94">
         <v>7.25</v>
@@ -4348,27 +4336,27 @@
         <v>6.39</v>
       </c>
       <c r="F94" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G94" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H94" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I94" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B95" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C95" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D95">
         <v>6.96</v>
@@ -4377,27 +4365,27 @@
         <v>6.18</v>
       </c>
       <c r="F95" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G95" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H95" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I95" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B96" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C96" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D96">
         <v>7.75</v>
@@ -4406,27 +4394,27 @@
         <v>7.54</v>
       </c>
       <c r="F96" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G96" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H96" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I96" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B97" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C97" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D97">
         <v>7.04</v>
@@ -4435,27 +4423,27 @@
         <v>6.69</v>
       </c>
       <c r="F97" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G97" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H97" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I97" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B98" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C98" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D98">
         <v>7.21</v>
@@ -4464,27 +4452,27 @@
         <v>6.9</v>
       </c>
       <c r="F98" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G98" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H98" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I98" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B99" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C99" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D99">
         <v>8.08</v>
@@ -4493,27 +4481,27 @@
         <v>7.39</v>
       </c>
       <c r="F99" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G99" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H99" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I99" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B100" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C100" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D100">
         <v>6.75</v>
@@ -4522,27 +4510,27 @@
         <v>6.31</v>
       </c>
       <c r="F100" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H100" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B101" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C101" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D101">
         <v>5.83</v>
@@ -4551,27 +4539,27 @@
         <v>5.84</v>
       </c>
       <c r="F101" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G101" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H101" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I101" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B102" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C102" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D102">
         <v>5.58</v>
@@ -4580,27 +4568,27 @@
         <v>5.33</v>
       </c>
       <c r="F102" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G102" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H102" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I102" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B103" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C103" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D103">
         <v>6.79</v>
@@ -4609,27 +4597,27 @@
         <v>7.21</v>
       </c>
       <c r="F103" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G103" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H103" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I103" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B104" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C104" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D104">
         <v>7.33</v>
@@ -4638,27 +4626,27 @@
         <v>7.2</v>
       </c>
       <c r="F104" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H104" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I104" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B105" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C105" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D105">
         <v>8.33</v>
@@ -4667,16 +4655,16 @@
         <v>7.91</v>
       </c>
       <c r="F105" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G105" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H105" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I105" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4714,27 +4702,27 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>8.5</v>
@@ -4743,27 +4731,27 @@
         <v>7.13</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>8.33</v>
@@ -4772,27 +4760,27 @@
         <v>7.39</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
       <c r="I3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>8.33</v>
@@ -4801,27 +4789,27 @@
         <v>7.91</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>8.2100000000000009</v>
@@ -4830,27 +4818,27 @@
         <v>7.91</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>8.17</v>
@@ -4859,27 +4847,27 @@
         <v>7.56</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>8.08</v>
@@ -4888,27 +4876,27 @@
         <v>7.39</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>8.08</v>
@@ -4917,27 +4905,27 @@
         <v>7.47</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>8.08</v>
@@ -4946,27 +4934,27 @@
         <v>7.39</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B10" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>8.0399999999999991</v>
@@ -4975,27 +4963,27 @@
         <v>7.77</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>7.96</v>
@@ -5004,27 +4992,27 @@
         <v>6.98</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>7.96</v>
@@ -5033,27 +5021,27 @@
         <v>7.68</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>7.92</v>
@@ -5062,27 +5050,27 @@
         <v>7.43</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I13" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B14" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D14">
         <v>7.88</v>
@@ -5091,27 +5079,27 @@
         <v>7.31</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <v>7.79</v>
@@ -5120,27 +5108,27 @@
         <v>6.62</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>7.75</v>
@@ -5149,27 +5137,27 @@
         <v>7.33</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H16" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I16" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>7.75</v>
@@ -5178,27 +5166,27 @@
         <v>7.54</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H17" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I17" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B18" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D18">
         <v>7.71</v>
@@ -5207,27 +5195,27 @@
         <v>7.03</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B19" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <v>7.71</v>
@@ -5236,27 +5224,27 @@
         <v>7.18</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>7.71</v>
@@ -5265,27 +5253,27 @@
         <v>7.3</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>7.54</v>
@@ -5294,27 +5282,27 @@
         <v>6.86</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H21" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <v>7.54</v>
@@ -5323,27 +5311,27 @@
         <v>6.6</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G22" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>7.54</v>
@@ -5352,27 +5340,27 @@
         <v>6.89</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H23" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D24">
         <v>7.5</v>
@@ -5381,27 +5369,27 @@
         <v>6.96</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G24" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I24" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B25" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D25">
         <v>7.5</v>
@@ -5410,27 +5398,27 @@
         <v>6.38</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G25" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H25" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I25" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>7.46</v>
@@ -5439,27 +5427,27 @@
         <v>6.76</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G26" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B27" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <v>7.46</v>
@@ -5468,27 +5456,27 @@
         <v>6.81</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B28" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D28">
         <v>7.42</v>
@@ -5497,27 +5485,27 @@
         <v>6.09</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G28" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H28" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I28" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B29" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D29">
         <v>7.42</v>
@@ -5526,27 +5514,27 @@
         <v>6.56</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G29" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I29" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>7.38</v>
@@ -5555,27 +5543,27 @@
         <v>6.74</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I30" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B31" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <v>7.38</v>
@@ -5584,27 +5572,27 @@
         <v>6.8</v>
       </c>
       <c r="F31" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G31" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H31" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I31" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B32" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D32">
         <v>7.38</v>
@@ -5613,27 +5601,27 @@
         <v>6.79</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H32" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I32" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B33" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D33">
         <v>7.38</v>
@@ -5642,27 +5630,27 @@
         <v>6.93</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H33" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B34" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C34" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D34">
         <v>7.33</v>
@@ -5671,27 +5659,27 @@
         <v>7.2</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H34" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B35" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D35">
         <v>7.29</v>
@@ -5700,27 +5688,27 @@
         <v>6.41</v>
       </c>
       <c r="F35" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G35" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I35" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B36" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D36">
         <v>7.25</v>
@@ -5729,27 +5717,27 @@
         <v>6.39</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I36" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B37" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C37" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D37">
         <v>7.21</v>
@@ -5758,27 +5746,27 @@
         <v>6.9</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D38">
         <v>7.17</v>
@@ -5787,27 +5775,27 @@
         <v>6.48</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B39" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D39">
         <v>7.17</v>
@@ -5816,27 +5804,27 @@
         <v>6.44</v>
       </c>
       <c r="F39" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H39" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I39" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B40" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D40">
         <v>7.17</v>
@@ -5845,27 +5833,27 @@
         <v>6.68</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I40" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C41" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <v>7.17</v>
@@ -5874,27 +5862,27 @@
         <v>6.33</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I41" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B42" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D42">
         <v>7.17</v>
@@ -5903,27 +5891,27 @@
         <v>6.66</v>
       </c>
       <c r="F42" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G42" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H42" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I42" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D43">
         <v>7.08</v>
@@ -5932,27 +5920,27 @@
         <v>7.09</v>
       </c>
       <c r="F43" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G43" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H43" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C44" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D44">
         <v>7.04</v>
@@ -5961,27 +5949,27 @@
         <v>6.51</v>
       </c>
       <c r="F44" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G44" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H44" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I44" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B45" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D45">
         <v>7.04</v>
@@ -5990,27 +5978,27 @@
         <v>6.12</v>
       </c>
       <c r="F45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B46" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D46">
         <v>7.04</v>
@@ -6019,27 +6007,27 @@
         <v>6.3</v>
       </c>
       <c r="F46" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B47" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C47" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D47">
         <v>7.04</v>
@@ -6048,27 +6036,27 @@
         <v>6.69</v>
       </c>
       <c r="F47" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G47" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H47" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I47" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C48" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D48">
         <v>7</v>
@@ -6077,27 +6065,27 @@
         <v>6.3</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H48" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B49" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D49">
         <v>6.96</v>
@@ -6106,27 +6094,27 @@
         <v>6.83</v>
       </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G49" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H49" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B50" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C50" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D50">
         <v>6.96</v>
@@ -6135,27 +6123,27 @@
         <v>6.18</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B51" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C51" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D51">
         <v>6.88</v>
@@ -6164,27 +6152,27 @@
         <v>6.71</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C52" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D52">
         <v>6.79</v>
@@ -6193,27 +6181,27 @@
         <v>5.96</v>
       </c>
       <c r="F52" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H52" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B53" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C53" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D53">
         <v>6.79</v>
@@ -6222,27 +6210,27 @@
         <v>7.21</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H53" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C54" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D54">
         <v>6.75</v>
@@ -6251,27 +6239,27 @@
         <v>6.35</v>
       </c>
       <c r="F54" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G54" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H54" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B55" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C55" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D55">
         <v>6.75</v>
@@ -6280,27 +6268,27 @@
         <v>6.31</v>
       </c>
       <c r="F55" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H55" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I55" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B56" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C56" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D56">
         <v>6.63</v>
@@ -6309,27 +6297,27 @@
         <v>6.26</v>
       </c>
       <c r="F56" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G56" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H56" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B57" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C57" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D57">
         <v>6.63</v>
@@ -6338,27 +6326,27 @@
         <v>5.71</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B58" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C58" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D58">
         <v>6.38</v>
@@ -6367,27 +6355,27 @@
         <v>6.1</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G58" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H58" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C59" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D59">
         <v>6.38</v>
@@ -6396,27 +6384,27 @@
         <v>5.96</v>
       </c>
       <c r="F59" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B60" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C60" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D60">
         <v>6.33</v>
@@ -6425,27 +6413,27 @@
         <v>6.25</v>
       </c>
       <c r="F60" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G60" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H60" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B61" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C61" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D61">
         <v>6.33</v>
@@ -6454,27 +6442,27 @@
         <v>5.95</v>
       </c>
       <c r="F61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B62" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C62" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D62">
         <v>6.29</v>
@@ -6483,27 +6471,27 @@
         <v>6.25</v>
       </c>
       <c r="F62" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G62" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H62" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B63" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C63" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D63">
         <v>6.17</v>
@@ -6512,27 +6500,27 @@
         <v>5.34</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I63" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B64" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C64" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D64">
         <v>6.13</v>
@@ -6541,27 +6529,27 @@
         <v>6</v>
       </c>
       <c r="F64" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H64" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I64" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B65" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C65" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D65">
         <v>6.13</v>
@@ -6570,27 +6558,27 @@
         <v>6.05</v>
       </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G65" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H65" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I65" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B66" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C66" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D66">
         <v>6.04</v>
@@ -6599,27 +6587,27 @@
         <v>5.55</v>
       </c>
       <c r="F66" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H66" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B67" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C67" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D67">
         <v>5.96</v>
@@ -6628,27 +6616,27 @@
         <v>5.79</v>
       </c>
       <c r="F67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B68" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C68" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D68">
         <v>5.83</v>
@@ -6657,27 +6645,27 @@
         <v>5.84</v>
       </c>
       <c r="F68" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G68" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I68" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B69" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C69" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D69">
         <v>5.58</v>
@@ -6686,27 +6674,27 @@
         <v>5.69</v>
       </c>
       <c r="F69" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H69" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B70" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C70" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D70">
         <v>5.58</v>
@@ -6715,27 +6703,27 @@
         <v>5.33</v>
       </c>
       <c r="F70" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G70" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H70" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B71" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C71" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D71">
         <v>5.29</v>
@@ -6744,16 +6732,16 @@
         <v>5.19</v>
       </c>
       <c r="F71" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H71" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I71" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -6834,27 +6822,27 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>8.2100000000000009</v>
@@ -6863,27 +6851,27 @@
         <v>7.91</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>8.33</v>
@@ -6892,27 +6880,27 @@
         <v>7.91</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>8.0399999999999991</v>
@@ -6921,27 +6909,27 @@
         <v>7.77</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>7.96</v>
@@ -6950,27 +6938,27 @@
         <v>7.68</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>8.17</v>
@@ -6979,27 +6967,27 @@
         <v>7.56</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B7" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>7.75</v>
@@ -7008,27 +6996,27 @@
         <v>7.54</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>8.08</v>
@@ -7037,27 +7025,27 @@
         <v>7.47</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>7.92</v>
@@ -7066,27 +7054,27 @@
         <v>7.43</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>8.33</v>
@@ -7095,27 +7083,27 @@
         <v>7.39</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" t="s">
         <v>12</v>
       </c>
-      <c r="H10" t="s">
-        <v>16</v>
-      </c>
       <c r="I10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>8.08</v>
@@ -7124,27 +7112,27 @@
         <v>7.39</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B12" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>8.08</v>
@@ -7153,27 +7141,27 @@
         <v>7.39</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>7.75</v>
@@ -7182,27 +7170,27 @@
         <v>7.33</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B14" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D14">
         <v>7.88</v>
@@ -7211,27 +7199,27 @@
         <v>7.31</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <v>7.71</v>
@@ -7240,27 +7228,27 @@
         <v>7.3</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B16" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>6.79</v>
@@ -7269,27 +7257,27 @@
         <v>7.21</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B17" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>7.33</v>
@@ -7298,27 +7286,27 @@
         <v>7.2</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H17" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B18" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D18">
         <v>7.71</v>
@@ -7327,27 +7315,27 @@
         <v>7.18</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <v>8.5</v>
@@ -7356,27 +7344,27 @@
         <v>7.13</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>7.08</v>
@@ -7385,27 +7373,27 @@
         <v>7.09</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I20" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>7.71</v>
@@ -7414,27 +7402,27 @@
         <v>7.03</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B22" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <v>7.96</v>
@@ -7443,27 +7431,27 @@
         <v>6.98</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>7.5</v>
@@ -7472,27 +7460,27 @@
         <v>6.96</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G23" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I23" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B24" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D24">
         <v>7.38</v>
@@ -7501,27 +7489,27 @@
         <v>6.93</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G24" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H24" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B25" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D25">
         <v>7.21</v>
@@ -7530,27 +7518,27 @@
         <v>6.9</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H25" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I25" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B26" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>7.54</v>
@@ -7559,27 +7547,27 @@
         <v>6.89</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G26" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <v>7.54</v>
@@ -7588,27 +7576,27 @@
         <v>6.86</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H27" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B28" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D28">
         <v>6.96</v>
@@ -7617,27 +7605,27 @@
         <v>6.83</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G28" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D29">
         <v>7.46</v>
@@ -7646,27 +7634,27 @@
         <v>6.81</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H29" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B30" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>7.38</v>
@@ -7675,27 +7663,27 @@
         <v>6.8</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H30" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I30" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B31" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <v>7.38</v>
@@ -7704,27 +7692,27 @@
         <v>6.79</v>
       </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H31" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I31" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D32">
         <v>7.46</v>
@@ -7733,27 +7721,27 @@
         <v>6.76</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G32" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H32" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I32" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B33" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D33">
         <v>7.38</v>
@@ -7762,27 +7750,27 @@
         <v>6.74</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H33" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I33" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B34" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C34" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D34">
         <v>6.88</v>
@@ -7791,27 +7779,27 @@
         <v>6.71</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B35" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D35">
         <v>7.04</v>
@@ -7820,27 +7808,27 @@
         <v>6.69</v>
       </c>
       <c r="F35" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G35" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H35" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I35" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B36" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D36">
         <v>7.17</v>
@@ -7849,27 +7837,27 @@
         <v>6.68</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I36" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B37" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C37" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D37">
         <v>7.17</v>
@@ -7878,27 +7866,27 @@
         <v>6.66</v>
       </c>
       <c r="F37" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B38" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D38">
         <v>7.79</v>
@@ -7907,27 +7895,27 @@
         <v>6.62</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D39">
         <v>7.54</v>
@@ -7936,27 +7924,27 @@
         <v>6.6</v>
       </c>
       <c r="F39" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G39" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I39" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B40" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D40">
         <v>7.42</v>
@@ -7965,27 +7953,27 @@
         <v>6.56</v>
       </c>
       <c r="F40" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G40" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I40" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B41" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C41" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <v>7.04</v>
@@ -7994,27 +7982,27 @@
         <v>6.51</v>
       </c>
       <c r="F41" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G41" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B42" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D42">
         <v>7.17</v>
@@ -8023,27 +8011,27 @@
         <v>6.48</v>
       </c>
       <c r="F42" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G42" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H42" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I42" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B43" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D43">
         <v>7.17</v>
@@ -8052,27 +8040,27 @@
         <v>6.44</v>
       </c>
       <c r="F43" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H43" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I43" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B44" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C44" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D44">
         <v>7.29</v>
@@ -8081,27 +8069,27 @@
         <v>6.41</v>
       </c>
       <c r="F44" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G44" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H44" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I44" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B45" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D45">
         <v>7.25</v>
@@ -8110,27 +8098,27 @@
         <v>6.39</v>
       </c>
       <c r="F45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B46" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D46">
         <v>7.5</v>
@@ -8139,27 +8127,27 @@
         <v>6.38</v>
       </c>
       <c r="F46" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G46" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H46" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I46" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C47" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D47">
         <v>6.75</v>
@@ -8168,27 +8156,27 @@
         <v>6.35</v>
       </c>
       <c r="F47" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G47" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B48" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C48" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D48">
         <v>7.17</v>
@@ -8197,27 +8185,27 @@
         <v>6.33</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I48" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B49" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D49">
         <v>6.75</v>
@@ -8226,27 +8214,27 @@
         <v>6.31</v>
       </c>
       <c r="F49" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H49" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C50" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D50">
         <v>7</v>
@@ -8255,27 +8243,27 @@
         <v>6.3</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B51" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C51" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D51">
         <v>7.04</v>
@@ -8284,27 +8272,27 @@
         <v>6.3</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H51" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B52" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C52" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D52">
         <v>6.63</v>
@@ -8313,27 +8301,27 @@
         <v>6.26</v>
       </c>
       <c r="F52" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G52" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H52" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B53" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C53" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D53">
         <v>6.29</v>
@@ -8342,27 +8330,27 @@
         <v>6.25</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H53" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B54" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C54" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D54">
         <v>6.33</v>
@@ -8371,27 +8359,27 @@
         <v>6.25</v>
       </c>
       <c r="F54" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G54" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H54" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B55" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C55" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D55">
         <v>6.96</v>
@@ -8400,27 +8388,27 @@
         <v>6.18</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H55" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I55" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B56" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C56" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D56">
         <v>7.04</v>
@@ -8429,27 +8417,27 @@
         <v>6.12</v>
       </c>
       <c r="F56" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G56" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H56" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I56" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B57" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C57" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D57">
         <v>6.38</v>
@@ -8458,27 +8446,27 @@
         <v>6.1</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H57" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B58" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C58" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D58">
         <v>7.42</v>
@@ -8487,27 +8475,27 @@
         <v>6.09</v>
       </c>
       <c r="F58" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G58" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H58" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I58" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B59" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C59" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D59">
         <v>6.13</v>
@@ -8516,27 +8504,27 @@
         <v>6.05</v>
       </c>
       <c r="F59" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G59" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H59" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I59" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B60" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C60" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D60">
         <v>6.13</v>
@@ -8545,27 +8533,27 @@
         <v>6</v>
       </c>
       <c r="F60" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G60" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H60" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I60" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B61" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C61" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D61">
         <v>6.79</v>
@@ -8574,27 +8562,27 @@
         <v>5.96</v>
       </c>
       <c r="F61" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B62" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C62" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D62">
         <v>6.38</v>
@@ -8603,27 +8591,27 @@
         <v>5.96</v>
       </c>
       <c r="F62" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H62" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B63" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C63" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D63">
         <v>6.33</v>
@@ -8632,27 +8620,27 @@
         <v>5.95</v>
       </c>
       <c r="F63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I63" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B64" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C64" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D64">
         <v>5.83</v>
@@ -8661,27 +8649,27 @@
         <v>5.84</v>
       </c>
       <c r="F64" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G64" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H64" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I64" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B65" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C65" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D65">
         <v>5.96</v>
@@ -8690,27 +8678,27 @@
         <v>5.79</v>
       </c>
       <c r="F65" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H65" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B66" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C66" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D66">
         <v>6.63</v>
@@ -8719,27 +8707,27 @@
         <v>5.71</v>
       </c>
       <c r="F66" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G66" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H66" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B67" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C67" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D67">
         <v>5.58</v>
@@ -8748,27 +8736,27 @@
         <v>5.69</v>
       </c>
       <c r="F67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H67" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B68" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C68" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D68">
         <v>6.04</v>
@@ -8777,27 +8765,27 @@
         <v>5.55</v>
       </c>
       <c r="F68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B69" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C69" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D69">
         <v>6.17</v>
@@ -8806,27 +8794,27 @@
         <v>5.34</v>
       </c>
       <c r="F69" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G69" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I69" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B70" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C70" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D70">
         <v>5.58</v>
@@ -8835,27 +8823,27 @@
         <v>5.33</v>
       </c>
       <c r="F70" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G70" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H70" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B71" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C71" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D71">
         <v>5.29</v>
@@ -8864,16 +8852,16 @@
         <v>5.19</v>
       </c>
       <c r="F71" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H71" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I71" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
